--- a/college-posters/data/字段表_211第七批.xlsx
+++ b/college-posters/data/字段表_211第七批.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -505,68 +505,68 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>银行证券与基金、会计师事务所与咨询、互联网与金融科技</t>
+          <t>国定路校区：杨浦主校区；武川路校区：杨浦校区；图书馆：国定路校区标志建筑</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>上海财经大学</t>
+          <t>中央财经大学</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>国定路校区：杨浦主校区；武川路校区：杨浦校区；图书馆：国定路校区标志建筑</t>
+          <t>金融学、会计学、财政学、税收学、保险学、经济学</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>上海财经大学</t>
+          <t>中央财经大学</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>学院南路校区：海淀主校区；沙河校区：昌平新校区；主楼：学院南路校区标志建筑</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>中央财经大学</t>
+          <t>对外经济贸易大学</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>金融学、会计学、财政学、税收学、保险学、经济学</t>
+          <t>国际经济与贸易、金融学、会计学、法学、英语、商务英语</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -588,73 +588,73 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>中央财经大学</t>
+          <t>对外经济贸易大学</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>银行证券与基金、财税系统与党政机关、会计与咨询</t>
+          <t>惠新东街校区：朝阳主校区；诚信楼：校园标志建筑；图书馆：校园中心建筑</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>中央财经大学</t>
+          <t>中南财经政法大学</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>学院南路校区：海淀主校区；沙河校区：昌平新校区；主楼：学院南路校区标志建筑</t>
+          <t>法学、会计学、金融学、经济学、财政学、工商管理</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>中央财经大学</t>
+          <t>中南财经政法大学</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>南湖校区：武汉主校区；首义校区：老校区；文泉楼：南湖校区标志建筑</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>对外经济贸易大学</t>
+          <t>西南财经大学</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>国际经济与贸易、金融学、会计学、法学、英语、商务英语</t>
+          <t>金融学、会计学、经济学、保险学、统计学、财政学</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -676,73 +676,73 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>对外经济贸易大学</t>
+          <t>西南财经大学</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>外资与跨国企业、银行证券与金融、外贸与咨询</t>
+          <t>柳林校区：温江主校区；光华校区：成都市区老校区；图书馆：柳林校区标志建筑</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>对外经济贸易大学</t>
+          <t>北京外国语大学</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>惠新东街校区：朝阳主校区；诚信楼：校园标志建筑；图书馆：校园中心建筑</t>
+          <t>英语、翻译、外交学、法语、德语、非通用语种</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>对外经济贸易大学</t>
+          <t>北京外国语大学</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>东院：海淀主校区；西院：西三环北路校区；图书馆：东院标志建筑</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>中南财经政法大学</t>
+          <t>上海外国语大学</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>法学、会计学、金融学、经济学、财政学、工商管理</t>
+          <t>英语、翻译、新闻学、法语、日语、国际经济与贸易</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -764,73 +764,73 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>中南财经政法大学</t>
+          <t>上海外国语大学</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>法院检察院与律所、银行与会计、党政机关与国企</t>
+          <t>虹口校区：大连西路老校区；松江校区：松江大学城主校区；图书馆：松江校区标志建筑</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>中南财经政法大学</t>
+          <t>中国政法大学</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>南湖校区：武汉主校区；首义校区：老校区；文泉楼：南湖校区标志建筑</t>
+          <t>法学、政治学与行政学、社会学、新闻学、经济学、英语</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>中南财经政法大学</t>
+          <t>中国政法大学</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>学院路校区：海淀老校区；昌平校区：本科主校区；拓荒牛：昌平校区标志雕塑</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>西南财经大学</t>
+          <t>北京中医药大学</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>金融学、会计学、经济学、保险学、统计学、财政学</t>
+          <t>中医学、中药学、针灸推拿学、中西医临床医学、护理学、药学</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -852,73 +852,73 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>西南财经大学</t>
+          <t>北京中医药大学</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>银行证券与保险、会计与咨询、党政机关与国企</t>
+          <t>和平街校区：朝阳老校区；良乡校区：房山主校区；中医药博物馆：展示中医药文化</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>西南财经大学</t>
+          <t>北京中医药大学</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>柳林校区：温江主校区；光华校区：成都市区老校区；图书馆：柳林校区标志建筑</t>
+          <t>医学类专业物理+化学；初稿“部分省份可选历史”未核实，已删除</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>西南财经大学</t>
+          <t>中国药科大学</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>软科中国大学排名</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>软科2026医药类大学排名第10名（单一第三方来源）</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核（单一来源）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>北京外国语大学</t>
+          <t>中国药科大学</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>英语、翻译、外交学、法语、德语、非通用语种</t>
+          <t>药学、中药学、药物制剂、临床药学、生物制药、药物分析</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -940,440 +940,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>北京外国语大学</t>
+          <t>中国药科大学</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>外交与国际组织、外企与跨国公司、翻译与传媒</t>
+          <t>玄武门校区：南京城内老校区；江宁校区：江宁主校区；药用植物园：校园特色景观</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>北京外国语大学</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>东院：海淀主校区；西院：西三环北路校区；图书馆：东院标志建筑</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
           <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>北京外国语大学</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>文科类专业：要求较宽，以当年招生章程为准；理工类专业：物理 + 化学</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>上海外国语大学</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>英语、翻译、新闻学、法语、日语、国际经济与贸易</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>上海外国语大学</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>外企与跨国公司、翻译与传媒、国际组织与外事</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>上海外国语大学</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>虹口校区：大连西路老校区；松江校区：松江大学城主校区；图书馆：松江校区标志建筑</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>上海外国语大学</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>文科类专业：要求较宽，以当年招生章程为准；理工类专业：物理 + 化学</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>中国政法大学</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>法学、政治学与行政学、社会学、新闻学、经济学、英语</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>中国政法大学</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>法院检察院与公安、律师事务所、党政机关与企业法务</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>中国政法大学</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>学院路校区：海淀老校区；昌平校区：本科主校区；拓荒牛：昌平校区标志雕塑</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>中国政法大学</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>文科类专业：要求较宽，以当年招生章程为准；理工类专业：物理 + 化学</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>北京中医药大学</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>中医学、中药学、针灸推拿学、中西医临床医学、护理学、药学</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>北京中医药大学</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>中医医院、医药企业、科研与教育</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>北京中医药大学</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>和平街校区：朝阳老校区；良乡校区：房山主校区；中医药博物馆：展示中医药文化</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>北京中医药大学</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>医学类专业物理+化学；初稿“部分省份可选历史”未核实，已删除</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>中国药科大学</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>软科中国大学排名</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>软科2026医药类大学排名第10名（单一第三方来源）</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>待核（单一来源）</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>中国药科大学</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>药学、中药学、药物制剂、临床药学、生物制药、药物分析</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>中国药科大学</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>医药企业与研发、医院药剂、药监与检测</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>中国药科大学</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>玄武门校区：南京城内老校区；江宁校区：江宁主校区；药用植物园：校园特色景观</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>中国药科大学</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
@@ -1937,9 +1519,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2062,7 +1644,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -2695,9 +2277,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2820,12 +2402,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -3453,9 +3035,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3160,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -4211,9 +3793,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -4336,12 +3918,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -4969,9 +4551,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -5094,12 +4676,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -5727,9 +5309,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5434,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -6485,9 +6067,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -6610,12 +6192,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -7243,9 +6825,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -7368,12 +6950,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -8001,9 +7583,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -8126,12 +7708,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -8759,9 +8341,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -8884,12 +8466,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
